--- a/mist/new/Califlower_Calculators_v15.0/Califlower Calculator v15.xlsx
+++ b/mist/new/Califlower_Calculators_v15.0/Califlower Calculator v15.xlsx
@@ -773,23 +773,27 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -797,23 +801,23 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -825,7 +829,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -861,39 +865,39 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -901,51 +905,51 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -953,15 +957,15 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -969,51 +973,47 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1021,19 +1021,19 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1041,11 +1041,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1053,31 +1053,31 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1523,9 +1523,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>47160</xdr:colOff>
+      <xdr:colOff>46800</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>122760</xdr:rowOff>
+      <xdr:rowOff>122400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1538,8 +1538,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7955280" y="247680"/>
-          <a:ext cx="4851720" cy="4304880"/>
+          <a:off x="7955640" y="247680"/>
+          <a:ext cx="4851360" cy="4304520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1735,1131 +1735,1130 @@
   <dimension ref="A1:Q107"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="20.86"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="33.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" s="4" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+    <row r="3" s="5" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" s="4" customFormat="true" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3"/>
-      <c r="B4" s="5" t="s">
+    <row r="4" s="5" customFormat="true" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4"/>
+      <c r="B4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="6" t="n">
+      <c r="C4" s="7" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="5" s="4" customFormat="true" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3"/>
-      <c r="B5" s="7" t="s">
+    <row r="5" s="5" customFormat="true" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4"/>
+      <c r="B5" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="7"/>
+      <c r="D5" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8"/>
-      <c r="B7" s="9" t="s">
+      <c r="A7" s="9"/>
+      <c r="B7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="11" t="n">
+      <c r="A8" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="12" t="n">
+      <c r="B8" s="13" t="n">
+        <v>99.77</v>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>99.76</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>99.76</v>
+      </c>
+      <c r="E8" s="15" t="n">
+        <f aca="false">AVERAGE(B8:D8)</f>
+        <v>99.7633333333333</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="16" t="n">
+        <v>49.75</v>
+      </c>
+      <c r="C9" s="17" t="n">
+        <v>49.76</v>
+      </c>
+      <c r="D9" s="17" t="n">
+        <v>49.77</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <f aca="false">AVERAGE(B9:D9)</f>
+        <v>49.76</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="13" t="n">
+        <v>99.97</v>
+      </c>
+      <c r="C10" s="14" t="n">
+        <v>99.96</v>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>99.97</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <f aca="false">AVERAGE(B10:D10)</f>
+        <v>99.9666666666667</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="16" t="n">
+        <v>50.05</v>
+      </c>
+      <c r="C11" s="17" t="n">
+        <v>50.02</v>
+      </c>
+      <c r="D11" s="17" t="n">
+        <v>50.03</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <f aca="false">AVERAGE(B11:D11)</f>
+        <v>50.0333333333333</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="13" t="n">
         <v>99.8</v>
       </c>
-      <c r="C8" s="13" t="n">
+      <c r="C12" s="14" t="n">
         <v>99.8</v>
       </c>
-      <c r="D8" s="13" t="n">
-        <v>99.8</v>
-      </c>
-      <c r="E8" s="14" t="n">
-        <f aca="false">AVERAGE(B8:D8)</f>
-        <v>99.8</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" s="15" t="n">
-        <v>49.87</v>
-      </c>
-      <c r="C9" s="16" t="n">
-        <v>49.88</v>
-      </c>
-      <c r="D9" s="16" t="n">
-        <v>49.88</v>
-      </c>
-      <c r="E9" s="14" t="n">
-        <f aca="false">AVERAGE(B9:D9)</f>
-        <v>49.8766666666667</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="B10" s="12" t="n">
-        <v>99.88</v>
-      </c>
-      <c r="C10" s="13" t="n">
-        <v>99.9</v>
-      </c>
-      <c r="D10" s="13" t="n">
+      <c r="D12" s="14" t="n">
+        <v>99.78</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <f aca="false">AVERAGE(B12:D12)</f>
+        <v>99.7933333333333</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="16" t="n">
+        <v>49.78</v>
+      </c>
+      <c r="C13" s="17" t="n">
+        <v>49.76</v>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>49.77</v>
+      </c>
+      <c r="E13" s="15" t="n">
+        <f aca="false">AVERAGE(B13:D13)</f>
+        <v>49.77</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="13" t="n">
+        <v>99.95</v>
+      </c>
+      <c r="C14" s="14" t="n">
+        <v>99.95</v>
+      </c>
+      <c r="D14" s="14" t="n">
         <v>99.96</v>
       </c>
-      <c r="E10" s="14" t="n">
-        <f aca="false">AVERAGE(B10:D10)</f>
-        <v>99.9133333333333</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="B11" s="15" t="n">
-        <v>49.99</v>
-      </c>
-      <c r="C11" s="16" t="n">
-        <v>49.98</v>
-      </c>
-      <c r="D11" s="16" t="n">
-        <v>49.97</v>
-      </c>
-      <c r="E11" s="14" t="n">
-        <f aca="false">AVERAGE(B11:D11)</f>
-        <v>49.98</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="12" t="n">
-        <v>99.92</v>
-      </c>
-      <c r="C12" s="13" t="n">
-        <v>99.88</v>
-      </c>
-      <c r="D12" s="13" t="n">
-        <v>99.89</v>
-      </c>
-      <c r="E12" s="14" t="n">
-        <f aca="false">AVERAGE(B12:D12)</f>
-        <v>99.8966666666667</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="B13" s="15" t="n">
-        <v>49.96</v>
-      </c>
-      <c r="C13" s="16" t="n">
-        <v>49.98</v>
-      </c>
-      <c r="D13" s="16" t="n">
-        <v>49.98</v>
-      </c>
-      <c r="E13" s="14" t="n">
-        <f aca="false">AVERAGE(B13:D13)</f>
-        <v>49.9733333333333</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="B14" s="12" t="n">
-        <v>99.98</v>
-      </c>
-      <c r="C14" s="13" t="n">
-        <v>99.96</v>
-      </c>
-      <c r="D14" s="13" t="n">
-        <v>99.96</v>
-      </c>
-      <c r="E14" s="14" t="n">
+      <c r="E14" s="15" t="n">
         <f aca="false">AVERAGE(B14:D14)</f>
-        <v>99.9666666666667</v>
+        <v>99.9533333333333</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="11" t="n">
+      <c r="A15" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="15" t="n">
-        <v>49.98</v>
-      </c>
-      <c r="C15" s="16" t="n">
-        <v>49.97</v>
-      </c>
-      <c r="D15" s="16" t="n">
-        <v>49.98</v>
-      </c>
-      <c r="E15" s="14" t="n">
+      <c r="B15" s="16" t="n">
+        <v>50.04</v>
+      </c>
+      <c r="C15" s="17" t="n">
+        <v>50.05</v>
+      </c>
+      <c r="D15" s="17" t="n">
+        <v>50.06</v>
+      </c>
+      <c r="E15" s="15" t="n">
         <f aca="false">AVERAGE(B15:D15)</f>
-        <v>49.9766666666667</v>
+        <v>50.05</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="11" t="n">
+      <c r="A16" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="12" t="n">
-        <v>99.83</v>
-      </c>
-      <c r="C16" s="13" t="n">
+      <c r="B16" s="13" t="n">
         <v>99.73</v>
       </c>
-      <c r="D16" s="13" t="n">
+      <c r="C16" s="14" t="n">
+        <v>99.73</v>
+      </c>
+      <c r="D16" s="14" t="n">
+        <v>99.71</v>
+      </c>
+      <c r="E16" s="15" t="n">
+        <f aca="false">AVERAGE(B16:D16)</f>
+        <v>99.7233333333333</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="13" t="n">
+        <v>99.76</v>
+      </c>
+      <c r="C17" s="14" t="n">
+        <v>99.76</v>
+      </c>
+      <c r="D17" s="14" t="n">
         <v>99.75</v>
       </c>
-      <c r="E16" s="14" t="n">
-        <f aca="false">AVERAGE(B16:D16)</f>
-        <v>99.77</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="11" t="n">
+      <c r="E17" s="15" t="n">
+        <f aca="false">AVERAGE(B17:D17)</f>
+        <v>99.7566666666667</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="B17" s="12" t="n">
-        <v>99.76</v>
-      </c>
-      <c r="C17" s="13" t="n">
-        <v>99.76</v>
-      </c>
-      <c r="D17" s="13" t="n">
-        <v>99.77</v>
-      </c>
-      <c r="E17" s="14" t="n">
-        <f aca="false">AVERAGE(B17:D17)</f>
-        <v>99.7633333333333</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="19" t="s">
+      <c r="B20" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="20" t="s">
+      <c r="C20" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="21" t="s">
+      <c r="B21" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="C21" s="22" t="s">
+      <c r="C21" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="D21" s="22"/>
-      <c r="E21" s="22"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
     </row>
     <row r="23" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G23" s="23" t="s">
+      <c r="G23" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="H23" s="24"/>
-      <c r="I23" s="24"/>
-      <c r="J23" s="24"/>
-      <c r="K23" s="24"/>
-      <c r="L23" s="24"/>
-      <c r="M23" s="24"/>
-      <c r="N23" s="24"/>
-      <c r="O23" s="24"/>
-      <c r="P23" s="24"/>
-      <c r="Q23" s="25"/>
+      <c r="H23" s="25"/>
+      <c r="I23" s="25"/>
+      <c r="J23" s="25"/>
+      <c r="K23" s="25"/>
+      <c r="L23" s="25"/>
+      <c r="M23" s="25"/>
+      <c r="N23" s="25"/>
+      <c r="O23" s="25"/>
+      <c r="P23" s="25"/>
+      <c r="Q23" s="26"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="26"/>
-      <c r="B24" s="27" t="s">
+      <c r="A24" s="27"/>
+      <c r="B24" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="G24" s="28" t="s">
+      <c r="G24" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="Q24" s="29"/>
+      <c r="Q24" s="30"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="30" t="s">
+      <c r="A25" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="B25" s="31" t="n">
+      <c r="B25" s="32" t="n">
         <f aca="false">Data!B13</f>
-        <v>-0.00143333333333334</v>
-      </c>
-      <c r="C25" s="32" t="n">
+        <v>-0.00170833333333338</v>
+      </c>
+      <c r="C25" s="33" t="n">
         <f aca="false">B25*-1</f>
-        <v>0.00143333333333334</v>
-      </c>
-      <c r="G25" s="28" t="s">
+        <v>0.00170833333333338</v>
+      </c>
+      <c r="G25" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="Q25" s="29"/>
+      <c r="Q25" s="30"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="30" t="s">
+      <c r="A26" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="B26" s="31" t="n">
+      <c r="B26" s="32" t="n">
         <f aca="false">Data!C13</f>
-        <v>-0.000591666666666733</v>
-      </c>
-      <c r="C26" s="32" t="n">
+        <v>-0.00153333333333329</v>
+      </c>
+      <c r="C26" s="33" t="n">
         <f aca="false">B26*-1</f>
-        <v>0.000591666666666733</v>
-      </c>
-      <c r="G26" s="28" t="s">
+        <v>0.00153333333333329</v>
+      </c>
+      <c r="G26" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="Q26" s="29"/>
+      <c r="Q26" s="30"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="33"/>
-      <c r="G27" s="28" t="s">
+      <c r="A27" s="34"/>
+      <c r="G27" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="Q27" s="29"/>
+      <c r="Q27" s="30"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="26"/>
-      <c r="B28" s="9" t="s">
+      <c r="A28" s="27"/>
+      <c r="B28" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="C28" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="G28" s="28" t="s">
+      <c r="G28" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="Q28" s="29"/>
+      <c r="Q28" s="30"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="30" t="s">
+      <c r="A29" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="B29" s="34" t="n">
+      <c r="B29" s="35" t="n">
         <f aca="false">Data!B19</f>
-        <v>89.9961713416085</v>
-      </c>
-      <c r="G29" s="28" t="s">
+        <v>90.0191484094121</v>
+      </c>
+      <c r="G29" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="Q29" s="29"/>
+      <c r="Q29" s="30"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="30" t="s">
+      <c r="A30" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="B30" s="34" t="n">
+      <c r="B30" s="35" t="n">
         <f aca="false">Data!B20</f>
-        <v>-0.003828658391555</v>
-      </c>
-      <c r="C30" s="34" t="n">
+        <v>0.0191484094121108</v>
+      </c>
+      <c r="C30" s="35" t="n">
         <f aca="false">-B30</f>
-        <v>0.003828658391555</v>
-      </c>
-      <c r="G30" s="28" t="s">
+        <v>-0.0191484094121108</v>
+      </c>
+      <c r="G30" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="Q30" s="29"/>
+      <c r="Q30" s="30"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="35"/>
-      <c r="B31" s="34"/>
-      <c r="C31" s="34"/>
-      <c r="G31" s="36" t="s">
+      <c r="A31" s="36"/>
+      <c r="B31" s="35"/>
+      <c r="C31" s="35"/>
+      <c r="G31" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="H31" s="37"/>
-      <c r="I31" s="37"/>
-      <c r="J31" s="37"/>
-      <c r="K31" s="37"/>
-      <c r="L31" s="37"/>
-      <c r="M31" s="37"/>
-      <c r="N31" s="37"/>
-      <c r="O31" s="37"/>
-      <c r="P31" s="37"/>
-      <c r="Q31" s="38"/>
+      <c r="H31" s="38"/>
+      <c r="I31" s="38"/>
+      <c r="J31" s="38"/>
+      <c r="K31" s="38"/>
+      <c r="L31" s="38"/>
+      <c r="M31" s="38"/>
+      <c r="N31" s="38"/>
+      <c r="O31" s="38"/>
+      <c r="P31" s="38"/>
+      <c r="Q31" s="39"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="26"/>
-      <c r="B32" s="9" t="s">
+      <c r="A32" s="27"/>
+      <c r="B32" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C32" s="9" t="s">
+      <c r="C32" s="10" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="39" t="s">
+      <c r="A33" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="31" t="n">
+      <c r="B33" s="32" t="n">
         <f aca="false">Data!D13</f>
-        <v>-0.000516666666666694</v>
-      </c>
-      <c r="C33" s="32" t="n">
+        <v>0.000216666666666647</v>
+      </c>
+      <c r="C33" s="33" t="n">
         <f aca="false">B33*-1</f>
-        <v>0.000516666666666694</v>
-      </c>
-      <c r="G33" s="23" t="s">
+        <v>-0.000216666666666647</v>
+      </c>
+      <c r="G33" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="H33" s="24"/>
-      <c r="I33" s="24"/>
-      <c r="J33" s="24"/>
-      <c r="K33" s="24"/>
-      <c r="L33" s="24"/>
-      <c r="M33" s="24"/>
-      <c r="N33" s="24"/>
-      <c r="O33" s="25"/>
+      <c r="H33" s="25"/>
+      <c r="I33" s="25"/>
+      <c r="J33" s="25"/>
+      <c r="K33" s="25"/>
+      <c r="L33" s="25"/>
+      <c r="M33" s="25"/>
+      <c r="N33" s="25"/>
+      <c r="O33" s="26"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="39" t="s">
+      <c r="A34" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="B34" s="31" t="n">
+      <c r="B34" s="32" t="n">
         <f aca="false">Data!E13</f>
-        <v>-0.00150833333333338</v>
-      </c>
-      <c r="C34" s="32" t="n">
+        <v>-0.00345833333333331</v>
+      </c>
+      <c r="C34" s="33" t="n">
         <f aca="false">B34*-1</f>
-        <v>0.00150833333333338</v>
-      </c>
-      <c r="G34" s="28" t="s">
+        <v>0.00345833333333331</v>
+      </c>
+      <c r="G34" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="H34" s="40"/>
-      <c r="I34" s="40"/>
-      <c r="J34" s="40"/>
-      <c r="K34" s="40"/>
-      <c r="L34" s="40"/>
-      <c r="M34" s="40"/>
-      <c r="N34" s="40"/>
-      <c r="O34" s="41"/>
+      <c r="H34" s="41"/>
+      <c r="I34" s="41"/>
+      <c r="J34" s="41"/>
+      <c r="K34" s="41"/>
+      <c r="L34" s="41"/>
+      <c r="M34" s="41"/>
+      <c r="N34" s="41"/>
+      <c r="O34" s="42"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G35" s="28" t="s">
+      <c r="G35" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="H35" s="40"/>
-      <c r="I35" s="40"/>
-      <c r="J35" s="40"/>
-      <c r="K35" s="40"/>
-      <c r="L35" s="40"/>
-      <c r="M35" s="40"/>
-      <c r="N35" s="40"/>
-      <c r="O35" s="41"/>
+      <c r="H35" s="41"/>
+      <c r="I35" s="41"/>
+      <c r="J35" s="41"/>
+      <c r="K35" s="41"/>
+      <c r="L35" s="41"/>
+      <c r="M35" s="41"/>
+      <c r="N35" s="41"/>
+      <c r="O35" s="42"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G36" s="28" t="s">
+      <c r="G36" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="H36" s="40"/>
-      <c r="I36" s="40"/>
-      <c r="J36" s="40"/>
-      <c r="K36" s="40"/>
-      <c r="L36" s="40"/>
-      <c r="M36" s="40"/>
-      <c r="N36" s="40"/>
-      <c r="O36" s="41"/>
+      <c r="H36" s="41"/>
+      <c r="I36" s="41"/>
+      <c r="J36" s="41"/>
+      <c r="K36" s="41"/>
+      <c r="L36" s="41"/>
+      <c r="M36" s="41"/>
+      <c r="N36" s="41"/>
+      <c r="O36" s="42"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G37" s="42" t="s">
+      <c r="G37" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="H37" s="42"/>
-      <c r="I37" s="42"/>
-      <c r="J37" s="42"/>
-      <c r="K37" s="42"/>
-      <c r="L37" s="42"/>
-      <c r="M37" s="42"/>
-      <c r="N37" s="42"/>
-      <c r="O37" s="42"/>
+      <c r="H37" s="43"/>
+      <c r="I37" s="43"/>
+      <c r="J37" s="43"/>
+      <c r="K37" s="43"/>
+      <c r="L37" s="43"/>
+      <c r="M37" s="43"/>
+      <c r="N37" s="43"/>
+      <c r="O37" s="43"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="43" t="s">
+      <c r="A38" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="G38" s="42"/>
-      <c r="H38" s="42"/>
-      <c r="I38" s="42"/>
-      <c r="J38" s="42"/>
-      <c r="K38" s="42"/>
-      <c r="L38" s="42"/>
-      <c r="M38" s="42"/>
-      <c r="N38" s="42"/>
-      <c r="O38" s="42"/>
+      <c r="G38" s="43"/>
+      <c r="H38" s="43"/>
+      <c r="I38" s="43"/>
+      <c r="J38" s="43"/>
+      <c r="K38" s="43"/>
+      <c r="L38" s="43"/>
+      <c r="M38" s="43"/>
+      <c r="N38" s="43"/>
+      <c r="O38" s="43"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G39" s="42"/>
-      <c r="H39" s="42"/>
-      <c r="I39" s="42"/>
-      <c r="J39" s="42"/>
-      <c r="K39" s="42"/>
-      <c r="L39" s="42"/>
-      <c r="M39" s="42"/>
-      <c r="N39" s="42"/>
-      <c r="O39" s="42"/>
+      <c r="G39" s="43"/>
+      <c r="H39" s="43"/>
+      <c r="I39" s="43"/>
+      <c r="J39" s="43"/>
+      <c r="K39" s="43"/>
+      <c r="L39" s="43"/>
+      <c r="M39" s="43"/>
+      <c r="N39" s="43"/>
+      <c r="O39" s="43"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="44" t="s">
+      <c r="B40" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="C40" s="45" t="s">
+      <c r="C40" s="46" t="s">
         <v>43</v>
       </c>
-      <c r="D40" s="46"/>
-      <c r="E40" s="47" t="s">
+      <c r="D40" s="47"/>
+      <c r="E40" s="48" t="s">
         <v>44</v>
       </c>
-      <c r="G40" s="48"/>
-      <c r="H40" s="48"/>
-      <c r="I40" s="48"/>
-      <c r="J40" s="48"/>
-      <c r="K40" s="48"/>
-      <c r="L40" s="48"/>
-      <c r="M40" s="48"/>
-      <c r="N40" s="48"/>
+      <c r="G40" s="49"/>
+      <c r="H40" s="49"/>
+      <c r="I40" s="49"/>
+      <c r="J40" s="49"/>
+      <c r="K40" s="49"/>
+      <c r="L40" s="49"/>
+      <c r="M40" s="49"/>
+      <c r="N40" s="49"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="44" t="s">
+      <c r="B41" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="C41" s="49" t="str">
+      <c r="C41" s="50" t="str">
         <f aca="false">Data!A23</f>
-        <v>SET_SKEW XY=99.77,99.76,70.61</v>
-      </c>
-      <c r="D41" s="46"/>
-      <c r="E41" s="47" t="s">
+        <v>SET_SKEW XY=99.72,99.76,70.59</v>
+      </c>
+      <c r="D41" s="47"/>
+      <c r="E41" s="48" t="s">
         <v>46</v>
       </c>
-      <c r="H41" s="48"/>
-      <c r="I41" s="48"/>
-      <c r="J41" s="48"/>
-      <c r="K41" s="48"/>
-      <c r="L41" s="48"/>
-      <c r="M41" s="48"/>
-      <c r="N41" s="48"/>
+      <c r="H41" s="49"/>
+      <c r="I41" s="49"/>
+      <c r="J41" s="49"/>
+      <c r="K41" s="49"/>
+      <c r="L41" s="49"/>
+      <c r="M41" s="49"/>
+      <c r="N41" s="49"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="44" t="s">
+      <c r="B42" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="C42" s="49" t="str">
+      <c r="C42" s="50" t="str">
         <f aca="false">Data!A24</f>
         <v>SKEW_PROFILE SAVE=CaliFlower</v>
       </c>
-      <c r="D42" s="46"/>
-      <c r="E42" s="47" t="s">
+      <c r="D42" s="47"/>
+      <c r="E42" s="48" t="s">
         <v>46</v>
       </c>
-      <c r="H42" s="48"/>
-      <c r="I42" s="48"/>
-      <c r="J42" s="48"/>
-      <c r="K42" s="48"/>
-      <c r="L42" s="48"/>
-      <c r="M42" s="48"/>
-      <c r="N42" s="48"/>
+      <c r="H42" s="49"/>
+      <c r="I42" s="49"/>
+      <c r="J42" s="49"/>
+      <c r="K42" s="49"/>
+      <c r="L42" s="49"/>
+      <c r="M42" s="49"/>
+      <c r="N42" s="49"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="44" t="s">
+      <c r="B43" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="C43" s="45" t="s">
+      <c r="C43" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="D43" s="46"/>
-      <c r="E43" s="47" t="s">
+      <c r="D43" s="47"/>
+      <c r="E43" s="48" t="s">
         <v>46</v>
       </c>
-      <c r="H43" s="48"/>
-      <c r="I43" s="48"/>
-      <c r="J43" s="48"/>
-      <c r="K43" s="48"/>
-      <c r="L43" s="48"/>
-      <c r="M43" s="48"/>
-      <c r="N43" s="48"/>
+      <c r="H43" s="49"/>
+      <c r="I43" s="49"/>
+      <c r="J43" s="49"/>
+      <c r="K43" s="49"/>
+      <c r="L43" s="49"/>
+      <c r="M43" s="49"/>
+      <c r="N43" s="49"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="44" t="s">
+      <c r="B44" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="C44" s="45" t="s">
+      <c r="C44" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="D44" s="46"/>
-      <c r="E44" s="47" t="s">
+      <c r="D44" s="47"/>
+      <c r="E44" s="48" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="44" t="s">
+      <c r="B45" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="C45" s="45" t="s">
+      <c r="C45" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="D45" s="46"/>
-      <c r="E45" s="47" t="s">
+      <c r="D45" s="47"/>
+      <c r="E45" s="48" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="46"/>
-      <c r="C46" s="46"/>
-      <c r="D46" s="46"/>
-      <c r="E46" s="46"/>
+      <c r="B46" s="47"/>
+      <c r="C46" s="47"/>
+      <c r="D46" s="47"/>
+      <c r="E46" s="47"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="43" t="s">
+      <c r="A47" s="44" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="50" t="s">
+      <c r="B49" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="C49" s="51" t="str">
+      <c r="C49" s="52" t="str">
         <f aca="false">Data!A28</f>
         <v>if ENABLED(SKEW_CORRECTION)</v>
       </c>
-      <c r="E49" s="52" t="s">
+      <c r="E49" s="53" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="50" t="s">
+      <c r="B50" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="C50" s="51" t="str">
+      <c r="C50" s="52" t="str">
         <f aca="false">Data!A29</f>
-        <v> define XY_DIAG_AC 99.77</v>
-      </c>
-      <c r="E50" s="52" t="s">
+        <v> define XY_DIAG_AC 99.7233</v>
+      </c>
+      <c r="E50" s="53" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B51" s="50" t="s">
+      <c r="B51" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="C51" s="51" t="str">
+      <c r="C51" s="52" t="str">
         <f aca="false">Data!A30</f>
-        <v> define XY_DIAG_BD 99.7633</v>
-      </c>
-      <c r="E51" s="52" t="s">
+        <v> define XY_DIAG_BD 99.7567</v>
+      </c>
+      <c r="E51" s="53" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B52" s="50" t="s">
+      <c r="B52" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="C52" s="51" t="str">
+      <c r="C52" s="52" t="str">
         <f aca="false">Data!A31</f>
-        <v> define XY_SIDE_AD 70.6093</v>
-      </c>
-      <c r="E52" s="52" t="s">
+        <v> define XY_SIDE_AD 70.5899</v>
+      </c>
+      <c r="E52" s="53" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B53" s="50"/>
-      <c r="E53" s="52"/>
+      <c r="B53" s="51"/>
+      <c r="E53" s="53"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="43" t="s">
+      <c r="A54" s="44" t="s">
         <v>54</v>
       </c>
-      <c r="B54" s="50"/>
-      <c r="E54" s="52"/>
+      <c r="B54" s="51"/>
+      <c r="E54" s="53"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="43"/>
-      <c r="B55" s="50"/>
-      <c r="E55" s="52"/>
+      <c r="A55" s="44"/>
+      <c r="B55" s="51"/>
+      <c r="E55" s="53"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B56" s="50" t="s">
+      <c r="B56" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="C56" s="51" t="str">
+      <c r="C56" s="52" t="str">
         <f aca="false">Data!A28</f>
         <v>if ENABLED(SKEW_CORRECTION)</v>
       </c>
-      <c r="E56" s="52" t="s">
+      <c r="E56" s="53" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B57" s="50" t="s">
+      <c r="B57" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="C57" s="51" t="str">
+      <c r="C57" s="52" t="str">
         <f aca="false">Data!A32</f>
-        <v> define XY_SKEW_FACTOR -0.002576</v>
-      </c>
-      <c r="E57" s="52" t="s">
+        <v> define XY_SKEW_FACTOR -0.002294</v>
+      </c>
+      <c r="E57" s="53" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B58" s="50"/>
-      <c r="E58" s="52"/>
+      <c r="B58" s="51"/>
+      <c r="E58" s="53"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B59" s="50"/>
-      <c r="E59" s="52"/>
+      <c r="B59" s="51"/>
+      <c r="E59" s="53"/>
     </row>
     <row r="60" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="43" t="s">
+      <c r="A60" s="44" t="s">
         <v>55</v>
       </c>
-      <c r="B60" s="50"/>
-      <c r="E60" s="52"/>
-      <c r="G60" s="23" t="s">
+      <c r="B60" s="51"/>
+      <c r="E60" s="53"/>
+      <c r="G60" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="H60" s="24"/>
-      <c r="I60" s="24"/>
-      <c r="J60" s="24"/>
-      <c r="K60" s="24"/>
-      <c r="L60" s="24"/>
-      <c r="M60" s="24"/>
-      <c r="N60" s="25"/>
+      <c r="H60" s="25"/>
+      <c r="I60" s="25"/>
+      <c r="J60" s="25"/>
+      <c r="K60" s="25"/>
+      <c r="L60" s="25"/>
+      <c r="M60" s="25"/>
+      <c r="N60" s="26"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B61" s="50"/>
-      <c r="E61" s="52"/>
-      <c r="G61" s="53" t="s">
+      <c r="B61" s="51"/>
+      <c r="E61" s="53"/>
+      <c r="G61" s="54" t="s">
         <v>57</v>
       </c>
-      <c r="N61" s="29"/>
+      <c r="N61" s="30"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B62" s="44" t="s">
+      <c r="B62" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="C62" s="51" t="str">
+      <c r="C62" s="52" t="str">
         <f aca="false">Data!B40</f>
         <v>#define SKEW_CORRECTION_GCODE</v>
       </c>
-      <c r="E62" s="47" t="s">
+      <c r="E62" s="48" t="s">
         <v>59</v>
       </c>
-      <c r="G62" s="54" t="s">
+      <c r="G62" s="55" t="s">
         <v>60</v>
       </c>
-      <c r="H62" s="37"/>
-      <c r="I62" s="37"/>
-      <c r="J62" s="37"/>
-      <c r="K62" s="37"/>
-      <c r="L62" s="37"/>
-      <c r="M62" s="37"/>
-      <c r="N62" s="38"/>
+      <c r="H62" s="38"/>
+      <c r="I62" s="38"/>
+      <c r="J62" s="38"/>
+      <c r="K62" s="38"/>
+      <c r="L62" s="38"/>
+      <c r="M62" s="38"/>
+      <c r="N62" s="39"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B63" s="44" t="s">
+      <c r="B63" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="C63" s="51" t="str">
+      <c r="C63" s="52" t="str">
         <f aca="false">Data!B41</f>
-        <v>M852 I-0.002576</v>
-      </c>
-      <c r="E63" s="47" t="s">
+        <v>M852 I-0.002294</v>
+      </c>
+      <c r="E63" s="48" t="s">
         <v>46</v>
       </c>
-      <c r="G63" s="55"/>
-      <c r="H63" s="55"/>
-      <c r="I63" s="55"/>
-      <c r="J63" s="55"/>
-      <c r="K63" s="55"/>
-      <c r="L63" s="55"/>
-      <c r="M63" s="55"/>
-      <c r="N63" s="55"/>
+      <c r="G63" s="56"/>
+      <c r="H63" s="56"/>
+      <c r="I63" s="56"/>
+      <c r="J63" s="56"/>
+      <c r="K63" s="56"/>
+      <c r="L63" s="56"/>
+      <c r="M63" s="56"/>
+      <c r="N63" s="56"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B64" s="44" t="s">
+      <c r="B64" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="C64" s="51" t="str">
+      <c r="C64" s="52" t="str">
         <f aca="false">Data!B42</f>
         <v>M500</v>
       </c>
-      <c r="E64" s="47" t="s">
+      <c r="E64" s="48" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E65" s="52"/>
+      <c r="E65" s="53"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="43" t="s">
+      <c r="A66" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="E66" s="52"/>
+      <c r="E66" s="53"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E67" s="52"/>
+      <c r="E67" s="53"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B68" s="50" t="s">
+      <c r="B68" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="C68" s="51" t="str">
+      <c r="C68" s="52" t="str">
         <f aca="false">Data!A47</f>
-        <v>M556 S100 X-0.007</v>
-      </c>
-      <c r="E68" s="52" t="s">
+        <v>M556 S100 X0.033</v>
+      </c>
+      <c r="E68" s="53" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="43" t="s">
+      <c r="A70" s="44" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="52" t="s">
+      <c r="A71" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="G71" s="55"/>
-      <c r="H71" s="55"/>
-      <c r="I71" s="55"/>
-      <c r="J71" s="55"/>
-      <c r="K71" s="55"/>
-      <c r="L71" s="55"/>
-      <c r="M71" s="55"/>
-      <c r="N71" s="55"/>
+      <c r="G71" s="56"/>
+      <c r="H71" s="56"/>
+      <c r="I71" s="56"/>
+      <c r="J71" s="56"/>
+      <c r="K71" s="56"/>
+      <c r="L71" s="56"/>
+      <c r="M71" s="56"/>
+      <c r="N71" s="56"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B72" s="56" t="s">
+      <c r="B72" s="57" t="s">
         <v>65</v>
       </c>
-      <c r="G72" s="55"/>
-      <c r="H72" s="55"/>
-      <c r="I72" s="55"/>
-      <c r="J72" s="55"/>
-      <c r="K72" s="55"/>
-      <c r="L72" s="55"/>
-      <c r="M72" s="55"/>
-      <c r="N72" s="55"/>
+      <c r="G72" s="56"/>
+      <c r="H72" s="56"/>
+      <c r="I72" s="56"/>
+      <c r="J72" s="56"/>
+      <c r="K72" s="56"/>
+      <c r="L72" s="56"/>
+      <c r="M72" s="56"/>
+      <c r="N72" s="56"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B73" s="50" t="s">
+      <c r="B73" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="C73" s="51" t="str">
+      <c r="C73" s="52" t="str">
         <f aca="false">Data!B51</f>
-        <v>M1005 X99.77 Y99.763</v>
-      </c>
-      <c r="E73" s="52" t="s">
+        <v>M1005 X99.723 Y99.757</v>
+      </c>
+      <c r="E73" s="53" t="s">
         <v>49</v>
       </c>
-      <c r="G73" s="55"/>
-      <c r="H73" s="55"/>
-      <c r="I73" s="55"/>
-      <c r="J73" s="55"/>
-      <c r="K73" s="55"/>
-      <c r="L73" s="55"/>
-      <c r="M73" s="55"/>
-      <c r="N73" s="55"/>
+      <c r="G73" s="56"/>
+      <c r="H73" s="56"/>
+      <c r="I73" s="56"/>
+      <c r="J73" s="56"/>
+      <c r="K73" s="56"/>
+      <c r="L73" s="56"/>
+      <c r="M73" s="56"/>
+      <c r="N73" s="56"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B74" s="50" t="s">
+      <c r="B74" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="C74" s="51" t="str">
+      <c r="C74" s="52" t="str">
         <f aca="false">Data!B53</f>
         <v>M500</v>
       </c>
-      <c r="E74" s="52" t="s">
+      <c r="E74" s="53" t="s">
         <v>49</v>
       </c>
-      <c r="G74" s="55"/>
-      <c r="H74" s="55"/>
-      <c r="I74" s="55"/>
-      <c r="J74" s="55"/>
-      <c r="K74" s="55"/>
-      <c r="L74" s="55"/>
-      <c r="M74" s="55"/>
-      <c r="N74" s="55"/>
+      <c r="G74" s="56"/>
+      <c r="H74" s="56"/>
+      <c r="I74" s="56"/>
+      <c r="J74" s="56"/>
+      <c r="K74" s="56"/>
+      <c r="L74" s="56"/>
+      <c r="M74" s="56"/>
+      <c r="N74" s="56"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B75" s="50" t="s">
+      <c r="B75" s="51" t="s">
         <v>66</v>
       </c>
-      <c r="C75" s="51"/>
-      <c r="E75" s="52"/>
-      <c r="G75" s="55"/>
-      <c r="H75" s="55"/>
-      <c r="I75" s="55"/>
-      <c r="J75" s="55"/>
-      <c r="K75" s="55"/>
-      <c r="L75" s="55"/>
-      <c r="M75" s="55"/>
-      <c r="N75" s="55"/>
+      <c r="C75" s="52"/>
+      <c r="E75" s="53"/>
+      <c r="G75" s="56"/>
+      <c r="H75" s="56"/>
+      <c r="I75" s="56"/>
+      <c r="J75" s="56"/>
+      <c r="K75" s="56"/>
+      <c r="L75" s="56"/>
+      <c r="M75" s="56"/>
+      <c r="N75" s="56"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B76" s="50" t="s">
+      <c r="B76" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="G76" s="55"/>
-      <c r="H76" s="55"/>
-      <c r="I76" s="55"/>
-      <c r="J76" s="55"/>
-      <c r="K76" s="55"/>
-      <c r="L76" s="55"/>
-      <c r="M76" s="55"/>
-      <c r="N76" s="55"/>
+      <c r="G76" s="56"/>
+      <c r="H76" s="56"/>
+      <c r="I76" s="56"/>
+      <c r="J76" s="56"/>
+      <c r="K76" s="56"/>
+      <c r="L76" s="56"/>
+      <c r="M76" s="56"/>
+      <c r="N76" s="56"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B77" s="50" t="s">
+      <c r="B77" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="C77" s="0" t="s">
+      <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E77" s="52"/>
-      <c r="G77" s="55"/>
-      <c r="H77" s="55"/>
-      <c r="I77" s="55"/>
-      <c r="J77" s="55"/>
-      <c r="K77" s="55"/>
-      <c r="L77" s="55"/>
-      <c r="M77" s="55"/>
-      <c r="N77" s="55"/>
+      <c r="E77" s="53"/>
+      <c r="G77" s="56"/>
+      <c r="H77" s="56"/>
+      <c r="I77" s="56"/>
+      <c r="J77" s="56"/>
+      <c r="K77" s="56"/>
+      <c r="L77" s="56"/>
+      <c r="M77" s="56"/>
+      <c r="N77" s="56"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B78" s="50" t="s">
+      <c r="B78" s="51" t="s">
         <v>70</v>
       </c>
-      <c r="C78" s="0" t="s">
+      <c r="C78" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E78" s="52" t="s">
+      <c r="E78" s="53" t="s">
         <v>72</v>
       </c>
-      <c r="G78" s="55"/>
-      <c r="H78" s="55"/>
-      <c r="I78" s="55"/>
-      <c r="J78" s="55"/>
-      <c r="K78" s="55"/>
-      <c r="L78" s="55"/>
-      <c r="M78" s="55"/>
-      <c r="N78" s="55"/>
+      <c r="G78" s="56"/>
+      <c r="H78" s="56"/>
+      <c r="I78" s="56"/>
+      <c r="J78" s="56"/>
+      <c r="K78" s="56"/>
+      <c r="L78" s="56"/>
+      <c r="M78" s="56"/>
+      <c r="N78" s="56"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B79" s="50"/>
-      <c r="E79" s="52"/>
-      <c r="G79" s="55"/>
-      <c r="H79" s="55"/>
-      <c r="I79" s="55"/>
-      <c r="J79" s="55"/>
-      <c r="K79" s="55"/>
-      <c r="L79" s="55"/>
-      <c r="M79" s="55"/>
-      <c r="N79" s="55"/>
+      <c r="B79" s="51"/>
+      <c r="E79" s="53"/>
+      <c r="G79" s="56"/>
+      <c r="H79" s="56"/>
+      <c r="I79" s="56"/>
+      <c r="J79" s="56"/>
+      <c r="K79" s="56"/>
+      <c r="L79" s="56"/>
+      <c r="M79" s="56"/>
+      <c r="N79" s="56"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B80" s="57" t="s">
+      <c r="B80" s="58" t="s">
         <v>73</v>
       </c>
-      <c r="E80" s="52"/>
-      <c r="G80" s="55"/>
-      <c r="H80" s="55"/>
-      <c r="I80" s="55"/>
-      <c r="J80" s="55"/>
-      <c r="K80" s="55"/>
-      <c r="L80" s="55"/>
-      <c r="M80" s="55"/>
-      <c r="N80" s="55"/>
+      <c r="E80" s="53"/>
+      <c r="G80" s="56"/>
+      <c r="H80" s="56"/>
+      <c r="I80" s="56"/>
+      <c r="J80" s="56"/>
+      <c r="K80" s="56"/>
+      <c r="L80" s="56"/>
+      <c r="M80" s="56"/>
+      <c r="N80" s="56"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B81" s="50" t="s">
+      <c r="B81" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="C81" s="51" t="str">
+      <c r="C81" s="52" t="str">
         <f aca="false">Data!B52</f>
         <v>M1005 I0</v>
       </c>
-      <c r="E81" s="52" t="s">
+      <c r="E81" s="53" t="s">
         <v>49</v>
       </c>
-      <c r="G81" s="55"/>
-      <c r="H81" s="55"/>
-      <c r="I81" s="55"/>
-      <c r="J81" s="55"/>
-      <c r="K81" s="55"/>
-      <c r="L81" s="55"/>
-      <c r="M81" s="55"/>
-      <c r="N81" s="55"/>
+      <c r="G81" s="56"/>
+      <c r="H81" s="56"/>
+      <c r="I81" s="56"/>
+      <c r="J81" s="56"/>
+      <c r="K81" s="56"/>
+      <c r="L81" s="56"/>
+      <c r="M81" s="56"/>
+      <c r="N81" s="56"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B82" s="50" t="s">
+      <c r="B82" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="C82" s="51" t="str">
+      <c r="C82" s="52" t="str">
         <f aca="false">Data!B53</f>
         <v>M500</v>
       </c>
-      <c r="E82" s="52" t="s">
+      <c r="E82" s="53" t="s">
         <v>49</v>
       </c>
-      <c r="G82" s="55"/>
-      <c r="H82" s="55"/>
-      <c r="I82" s="55"/>
-      <c r="J82" s="55"/>
-      <c r="K82" s="55"/>
-      <c r="L82" s="55"/>
-      <c r="M82" s="55"/>
-      <c r="N82" s="55"/>
+      <c r="G82" s="56"/>
+      <c r="H82" s="56"/>
+      <c r="I82" s="56"/>
+      <c r="J82" s="56"/>
+      <c r="K82" s="56"/>
+      <c r="L82" s="56"/>
+      <c r="M82" s="56"/>
+      <c r="N82" s="56"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B83" s="50" t="s">
+      <c r="B83" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="C83" s="58"/>
-      <c r="E83" s="52"/>
-      <c r="G83" s="55"/>
-      <c r="H83" s="55"/>
-      <c r="I83" s="55"/>
-      <c r="J83" s="55"/>
-      <c r="K83" s="55"/>
-      <c r="L83" s="55"/>
-      <c r="M83" s="55"/>
-      <c r="N83" s="55"/>
+      <c r="E83" s="53"/>
+      <c r="G83" s="56"/>
+      <c r="H83" s="56"/>
+      <c r="I83" s="56"/>
+      <c r="J83" s="56"/>
+      <c r="K83" s="56"/>
+      <c r="L83" s="56"/>
+      <c r="M83" s="56"/>
+      <c r="N83" s="56"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B84" s="50" t="s">
+      <c r="B84" s="51" t="s">
         <v>74</v>
       </c>
       <c r="C84" s="59" t="s">
         <v>75</v>
       </c>
-      <c r="E84" s="52" t="s">
+      <c r="E84" s="53" t="s">
         <v>76</v>
       </c>
-      <c r="G84" s="55"/>
-      <c r="H84" s="55"/>
-      <c r="I84" s="55"/>
-      <c r="J84" s="55"/>
-      <c r="K84" s="55"/>
-      <c r="L84" s="55"/>
-      <c r="M84" s="55"/>
-      <c r="N84" s="55"/>
+      <c r="G84" s="56"/>
+      <c r="H84" s="56"/>
+      <c r="I84" s="56"/>
+      <c r="J84" s="56"/>
+      <c r="K84" s="56"/>
+      <c r="L84" s="56"/>
+      <c r="M84" s="56"/>
+      <c r="N84" s="56"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B85" s="50"/>
+      <c r="B85" s="51"/>
       <c r="C85" s="59"/>
-      <c r="E85" s="52"/>
-      <c r="G85" s="55"/>
-      <c r="H85" s="55"/>
-      <c r="I85" s="55"/>
-      <c r="J85" s="55"/>
-      <c r="K85" s="55"/>
-      <c r="L85" s="55"/>
-      <c r="M85" s="55"/>
-      <c r="N85" s="55"/>
+      <c r="E85" s="53"/>
+      <c r="G85" s="56"/>
+      <c r="H85" s="56"/>
+      <c r="I85" s="56"/>
+      <c r="J85" s="56"/>
+      <c r="K85" s="56"/>
+      <c r="L85" s="56"/>
+      <c r="M85" s="56"/>
+      <c r="N85" s="56"/>
     </row>
     <row r="86" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="2" t="s">
+      <c r="A86" s="3" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="43" t="s">
+      <c r="A87" s="44" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B89" s="52" t="s">
+      <c r="B89" s="53" t="s">
         <v>79</v>
       </c>
-      <c r="C89" s="13" t="n">
+      <c r="C89" s="14" t="n">
         <f aca="false">Data!B56</f>
-        <v>99.9</v>
+        <v>99.84</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B90" s="52" t="s">
+      <c r="B90" s="53" t="s">
         <v>80</v>
       </c>
-      <c r="C90" s="13"/>
+      <c r="C90" s="14"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B91" s="52" t="s">
+      <c r="B91" s="53" t="s">
         <v>81</v>
       </c>
-      <c r="C91" s="13" t="n">
+      <c r="C91" s="14" t="n">
         <f aca="false">Data!B57</f>
-        <v>100.1</v>
+        <v>100.16</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="43" t="s">
+      <c r="A93" s="44" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B94" s="26"/>
+      <c r="B94" s="27"/>
       <c r="C94" s="60" t="s">
         <v>83</v>
       </c>
@@ -2889,9 +2888,9 @@
       <c r="B98" s="61" t="s">
         <v>86</v>
       </c>
-      <c r="C98" s="14" t="n">
+      <c r="C98" s="15" t="n">
         <f aca="false">Data!B60</f>
-        <v>100.143333333333</v>
+        <v>100.170833333333</v>
       </c>
       <c r="E98" s="63"/>
     </row>
@@ -2899,13 +2898,13 @@
       <c r="B99" s="61" t="s">
         <v>87</v>
       </c>
-      <c r="C99" s="14" t="n">
+      <c r="C99" s="15" t="n">
         <f aca="false">Data!B61</f>
-        <v>100.059166666667</v>
+        <v>100.153333333333</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="43" t="s">
+      <c r="A101" s="44" t="s">
         <v>88</v>
       </c>
     </row>
@@ -2938,18 +2937,18 @@
       <c r="B106" s="61" t="s">
         <v>91</v>
       </c>
-      <c r="C106" s="14" t="n">
+      <c r="C106" s="15" t="n">
         <f aca="false">Data!B64</f>
-        <v>99.8566666666667</v>
+        <v>99.8291666666667</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B107" s="61" t="s">
         <v>92</v>
       </c>
-      <c r="C107" s="14" t="n">
+      <c r="C107" s="15" t="n">
         <f aca="false">Data!B65</f>
-        <v>99.9408333333333</v>
+        <v>99.8466666666667</v>
       </c>
     </row>
   </sheetData>
@@ -3051,7 +3050,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" operator="between" id="{A0AE3EDB-4EF8-451C-8BB9-9A68B8962EEB}">
+          <x14:cfRule type="cellIs" priority="2" operator="between" id="{E125E916-D1E9-4CD9-9B6C-B5CE739752FF}">
             <xm:f>Data!$B$2+1</xm:f>
             <x14:dxf>
               <font>
@@ -3064,7 +3063,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="3" operator="lessThan" id="{BBAB5212-66E6-4674-A580-1BC170D776EF}">
+          <x14:cfRule type="cellIs" priority="3" operator="lessThan" id="{6DEAE521-32C1-4A75-B55B-683C8F406426}">
             <xm:f>Data!$B$2-5</xm:f>
             <x14:dxf>
               <font>
@@ -3077,7 +3076,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="4" operator="greaterThan" id="{CC9A2CF1-83C1-46DB-B38F-2B90CDC3A3C1}">
+          <x14:cfRule type="cellIs" priority="4" operator="greaterThan" id="{7C31DAAE-6AF4-4C84-96E6-CCA94089ED79}">
             <xm:f>Data!$B$2+5</xm:f>
             <x14:dxf>
               <font>
@@ -3090,7 +3089,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="5" operator="greaterThan" id="{4FF413FD-AFDD-424E-AD91-EF353A2470DE}">
+          <x14:cfRule type="cellIs" priority="5" operator="greaterThan" id="{E116A5DB-F4AD-4C1E-B227-BCD52C21861F}">
             <xm:f>Data!$B$2+1</xm:f>
             <x14:dxf>
               <font>
@@ -3103,7 +3102,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="6" operator="lessThan" id="{63309890-3DEF-4739-B2C4-BD2036201285}">
+          <x14:cfRule type="cellIs" priority="6" operator="lessThan" id="{4E5B874C-D836-4E2D-9B42-79D2A9B42064}">
             <xm:f>Data!$B$2-1</xm:f>
             <x14:dxf>
               <font>
@@ -3119,7 +3118,7 @@
           <xm:sqref>B8:D8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="7" operator="greaterThan" id="{C146EC90-23A5-40D2-986A-B1FCE7E53051}">
+          <x14:cfRule type="cellIs" priority="7" operator="greaterThan" id="{FBD7325D-29E6-4D8F-8850-18F93921B3A6}">
             <xm:f>Data!$B$3+5</xm:f>
             <x14:dxf>
               <font>
@@ -3132,7 +3131,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="8" operator="lessThan" id="{AD7898ED-4BF0-4DCE-8276-AF65B53D85A3}">
+          <x14:cfRule type="cellIs" priority="8" operator="lessThan" id="{002FC83B-4FCB-4CA4-A063-EE9028335BD0}">
             <xm:f>Data!$B$3-5</xm:f>
             <x14:dxf>
               <font>
@@ -3145,7 +3144,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="9" operator="between" id="{528D83BD-688A-4DDE-BAEA-CD3E85D4632B}">
+          <x14:cfRule type="cellIs" priority="9" operator="between" id="{F8F637E9-A79A-4CFB-83E6-4BA195DEFD4D}">
             <xm:f>Data!$B$3+1</xm:f>
             <x14:dxf>
               <font>
@@ -3158,7 +3157,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="10" operator="greaterThan" id="{5A89E054-B0BC-4C8E-AFC0-AF6B335E5F7C}">
+          <x14:cfRule type="cellIs" priority="10" operator="greaterThan" id="{95528E7E-9232-4B41-A0AE-90A39B543081}">
             <xm:f>Data!$B$3+1</xm:f>
             <x14:dxf>
               <font>
@@ -3171,7 +3170,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="11" operator="lessThan" id="{14E520B9-5156-48BD-AAE5-2E6CF052975F}">
+          <x14:cfRule type="cellIs" priority="11" operator="lessThan" id="{1535B098-D579-41B8-826E-35E2D621C53E}">
             <xm:f>Data!$B$3-1</xm:f>
             <x14:dxf>
               <font>
@@ -3187,7 +3186,7 @@
           <xm:sqref>B9:D9 B11:D11 B13:D13 B15:D15</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="12" operator="between" id="{30F0ED86-4F6B-426B-A14E-F0CC846EB982}">
+          <x14:cfRule type="cellIs" priority="12" operator="between" id="{E0A69B6F-717D-4281-B87D-EF3B93CD881A}">
             <xm:f>Data!$B$2+1</xm:f>
             <x14:dxf>
               <font>
@@ -3200,7 +3199,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="13" operator="lessThan" id="{C264FBD9-718B-4D1E-842B-D9C29332413A}">
+          <x14:cfRule type="cellIs" priority="13" operator="lessThan" id="{C8CEA046-F730-4726-8B84-807EA1EBE78D}">
             <xm:f>Data!$B$2-5</xm:f>
             <x14:dxf>
               <font>
@@ -3213,7 +3212,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="14" operator="greaterThan" id="{53379F6D-CCE7-4A60-8F9A-7E35FEA9A616}">
+          <x14:cfRule type="cellIs" priority="14" operator="greaterThan" id="{789F5493-A6D7-4D4A-B439-3CD1635DB5E0}">
             <xm:f>Data!$B$2+5</xm:f>
             <x14:dxf>
               <font>
@@ -3226,7 +3225,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="15" operator="greaterThan" id="{D1C4DB9E-1586-4018-B160-45851B9634AB}">
+          <x14:cfRule type="cellIs" priority="15" operator="greaterThan" id="{F3E5DDB0-AB4A-4EA1-A022-C528F0D81950}">
             <xm:f>Data!$B$2+1</xm:f>
             <x14:dxf>
               <font>
@@ -3239,7 +3238,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="16" operator="lessThan" id="{E9392AC5-B0B3-4D43-9FC3-D717CF1ECFB9}">
+          <x14:cfRule type="cellIs" priority="16" operator="lessThan" id="{A5189F2A-972A-43AF-8F17-E77F1670413D}">
             <xm:f>Data!$B$2-1</xm:f>
             <x14:dxf>
               <font>
@@ -3255,7 +3254,7 @@
           <xm:sqref>B10:D10</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="17" operator="between" id="{96B0D5BE-69F7-4A10-88F1-274EDB8221B0}">
+          <x14:cfRule type="cellIs" priority="17" operator="between" id="{4EC47640-D9F7-4E48-81D5-9B8EF959C622}">
             <xm:f>Data!$B$2+1</xm:f>
             <x14:dxf>
               <font>
@@ -3268,7 +3267,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="18" operator="lessThan" id="{BA9BD09E-44FF-4CBF-8A44-C3F3903DB955}">
+          <x14:cfRule type="cellIs" priority="18" operator="lessThan" id="{676452FF-B7AF-49D9-8BA2-7FDD1326C220}">
             <xm:f>Data!$B$2-5</xm:f>
             <x14:dxf>
               <font>
@@ -3281,7 +3280,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="19" operator="greaterThan" id="{6CF5BE21-89AC-4BD1-8E1D-4068A18D67C1}">
+          <x14:cfRule type="cellIs" priority="19" operator="greaterThan" id="{5063885C-642B-4B90-AC28-E1C2F3B0EE1E}">
             <xm:f>Data!$B$2+5</xm:f>
             <x14:dxf>
               <font>
@@ -3294,7 +3293,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="20" operator="greaterThan" id="{C96F25FF-3BD3-4649-B713-8C5BF079C0CC}">
+          <x14:cfRule type="cellIs" priority="20" operator="greaterThan" id="{E478706E-4082-45F0-895F-8D1163962896}">
             <xm:f>Data!$B$2+1</xm:f>
             <x14:dxf>
               <font>
@@ -3307,7 +3306,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="21" operator="lessThan" id="{3EFD2B68-EC9E-427E-84CF-4670D3546F43}">
+          <x14:cfRule type="cellIs" priority="21" operator="lessThan" id="{96F691D0-4D85-4DDE-8D9F-7C39D8D53BEE}">
             <xm:f>Data!$B$2-1</xm:f>
             <x14:dxf>
               <font>
@@ -3323,7 +3322,7 @@
           <xm:sqref>B12:D12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="22" operator="between" id="{715A2820-3E49-4BA0-8278-717C2B208415}">
+          <x14:cfRule type="cellIs" priority="22" operator="between" id="{FD6D24C9-3050-4187-B412-9B732659F9D2}">
             <xm:f>Data!$B$2+1</xm:f>
             <x14:dxf>
               <font>
@@ -3336,7 +3335,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="23" operator="lessThan" id="{6AA02024-4F10-4E8F-8867-DA20AC77A840}">
+          <x14:cfRule type="cellIs" priority="23" operator="lessThan" id="{EA40C573-D681-4454-9159-55A6E46F26E2}">
             <xm:f>Data!$B$2-5</xm:f>
             <x14:dxf>
               <font>
@@ -3349,7 +3348,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="24" operator="greaterThan" id="{3E8A8E5A-1AAE-4D48-A62E-3774C47627B0}">
+          <x14:cfRule type="cellIs" priority="24" operator="greaterThan" id="{9C8FB02B-28D1-4B96-B9A7-15C6707B3FD4}">
             <xm:f>Data!$B$2+5</xm:f>
             <x14:dxf>
               <font>
@@ -3362,7 +3361,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="25" operator="greaterThan" id="{C4D4D823-21FF-4294-BCF9-444F6B2470B4}">
+          <x14:cfRule type="cellIs" priority="25" operator="greaterThan" id="{63E97E94-E826-47CE-9B46-E0D7A0BDDD1E}">
             <xm:f>Data!$B$2+1</xm:f>
             <x14:dxf>
               <font>
@@ -3375,7 +3374,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="26" operator="lessThan" id="{87C062B3-1951-406F-8777-88603FC4C0F6}">
+          <x14:cfRule type="cellIs" priority="26" operator="lessThan" id="{D614B89A-4A55-43C1-BCF1-7415DC503E70}">
             <xm:f>Data!$B$2-1</xm:f>
             <x14:dxf>
               <font>
@@ -3391,7 +3390,7 @@
           <xm:sqref>B14:D14</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="27" operator="between" id="{4B9E89B0-F5A3-496C-9DE7-B6D51E58D388}">
+          <x14:cfRule type="cellIs" priority="27" operator="between" id="{7AA82FC2-C7E1-45B0-B62E-7860B27CB1FF}">
             <xm:f>Data!$B$2+1</xm:f>
             <x14:dxf>
               <font>
@@ -3404,7 +3403,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="28" operator="lessThan" id="{587DF3A0-4170-4763-B88D-8B3BDDA65A6F}">
+          <x14:cfRule type="cellIs" priority="28" operator="lessThan" id="{4894A6B4-E22C-4029-B724-7BA0AFEB88CA}">
             <xm:f>Data!$B$2-5</xm:f>
             <x14:dxf>
               <font>
@@ -3417,7 +3416,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="29" operator="greaterThan" id="{F975B33B-6695-41C0-BF90-16A0F3AF2C98}">
+          <x14:cfRule type="cellIs" priority="29" operator="greaterThan" id="{2637978F-8BEA-4EA9-8A89-9C1F90C6F85A}">
             <xm:f>Data!$B$2+5</xm:f>
             <x14:dxf>
               <font>
@@ -3430,7 +3429,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="30" operator="greaterThan" id="{77CC962C-2239-4176-9E9F-17AF4F8453F8}">
+          <x14:cfRule type="cellIs" priority="30" operator="greaterThan" id="{B24F966C-1AAD-43FC-B2E0-738FAAA7607E}">
             <xm:f>Data!$B$2+1</xm:f>
             <x14:dxf>
               <font>
@@ -3443,7 +3442,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="31" operator="lessThan" id="{5E7EB098-7C42-4D5C-9745-935068CF92D9}">
+          <x14:cfRule type="cellIs" priority="31" operator="lessThan" id="{4D62638D-2960-4DC0-8E39-C9372B8C7BB8}">
             <xm:f>Data!$B$2-1</xm:f>
             <x14:dxf>
               <font>
@@ -3459,7 +3458,7 @@
           <xm:sqref>B16:D16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="32" operator="between" id="{80B0C463-323B-4CA4-8C99-CC99232E509A}">
+          <x14:cfRule type="cellIs" priority="32" operator="between" id="{829BF0F6-D742-42FB-8055-758F009E11BA}">
             <xm:f>Data!$B$2+1</xm:f>
             <x14:dxf>
               <font>
@@ -3472,7 +3471,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="33" operator="lessThan" id="{5D183052-C8D8-4D17-9821-C2AF2AED4A4D}">
+          <x14:cfRule type="cellIs" priority="33" operator="lessThan" id="{7B1094FC-B09C-4CB3-87ED-948ED55744EE}">
             <xm:f>Data!$B$2-5</xm:f>
             <x14:dxf>
               <font>
@@ -3485,7 +3484,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="34" operator="greaterThan" id="{BDB037C9-6065-46E8-A0DF-2931CF3835FA}">
+          <x14:cfRule type="cellIs" priority="34" operator="greaterThan" id="{B6D91F60-66C9-406D-A5C7-2E3078B346FC}">
             <xm:f>Data!$B$2+5</xm:f>
             <x14:dxf>
               <font>
@@ -3498,7 +3497,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="35" operator="greaterThan" id="{B2121AB8-FBE6-4177-9547-347BFDC7F120}">
+          <x14:cfRule type="cellIs" priority="35" operator="greaterThan" id="{27A3D330-6F7A-4117-A8AA-73D81A94E160}">
             <xm:f>Data!$B$2+1</xm:f>
             <x14:dxf>
               <font>
@@ -3511,7 +3510,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="36" operator="lessThan" id="{2FA0735F-8999-4810-9941-6AEBC566655F}">
+          <x14:cfRule type="cellIs" priority="36" operator="lessThan" id="{D5EB831F-991F-424B-B47A-67CD1A494760}">
             <xm:f>Data!$B$2-1</xm:f>
             <x14:dxf>
               <font>
@@ -3540,15 +3539,15 @@
   <dimension ref="A1:I65"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="9.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="9.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="14.43"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1" s="43" t="s">
+      <c r="B1" s="44" t="s">
         <v>93</v>
       </c>
       <c r="C1" s="66" t="s">
@@ -3556,107 +3555,107 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="43" t="n">
+      <c r="A2" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="1" t="n">
         <f aca="false">100*scale</f>
         <v>100</v>
       </c>
       <c r="C2" s="67" t="n">
         <f aca="false">(Calculator!E8-Data!B2)/B2</f>
-        <v>-0.00200000000000003</v>
+        <v>-0.00236666666666665</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="43" t="n">
+      <c r="A3" s="44" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <f aca="false">50*scale</f>
         <v>50</v>
       </c>
       <c r="C3" s="67" t="n">
         <f aca="false">(Calculator!E9-Data!B3)/B3</f>
-        <v>-0.0024666666666667</v>
+        <v>-0.00480000000000004</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="43" t="n">
+      <c r="A4" s="44" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="1" t="n">
         <f aca="false">100*scale</f>
         <v>100</v>
       </c>
       <c r="C4" s="67" t="n">
         <f aca="false">(Calculator!E10-Data!B4)/B4</f>
-        <v>-0.000866666666666589</v>
+        <v>-0.000333333333333457</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="43" t="n">
+      <c r="A5" s="44" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <f aca="false">50*scale</f>
         <v>50</v>
       </c>
       <c r="C5" s="67" t="n">
         <f aca="false">(Calculator!E11-Data!B5)/B5</f>
-        <v>-0.000400000000000063</v>
+        <v>0.000666666666666629</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="43" t="n">
+      <c r="A6" s="44" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="1" t="n">
         <f aca="false">100*scale</f>
         <v>100</v>
       </c>
       <c r="C6" s="67" t="n">
         <f aca="false">(Calculator!E12-Data!B6)/B6</f>
-        <v>-0.00103333333333339</v>
+        <v>-0.00206666666666663</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="43" t="n">
+      <c r="A7" s="44" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="1" t="n">
         <f aca="false">50*scale</f>
         <v>50</v>
       </c>
       <c r="C7" s="67" t="n">
         <f aca="false">(Calculator!E13-Data!B7)/B7</f>
-        <v>-0.000533333333333417</v>
+        <v>-0.00459999999999994</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="43" t="n">
+      <c r="A8" s="44" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="1" t="n">
         <f aca="false">100*scale</f>
         <v>100</v>
       </c>
       <c r="C8" s="67" t="n">
         <f aca="false">(Calculator!E14-Data!B8)/B8</f>
-        <v>-0.000333333333333457</v>
+        <v>-0.000466666666666669</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="43" t="n">
+      <c r="A9" s="44" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9" s="1" t="n">
         <f aca="false">50*scale</f>
         <v>50</v>
       </c>
       <c r="C9" s="67" t="n">
         <f aca="false">(Calculator!E15-Data!B9)/B9</f>
-        <v>-0.000466666666666669</v>
+        <v>0.00100000000000009</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3682,24 +3681,24 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="31" t="n">
+      <c r="B13" s="32" t="n">
         <f aca="false">AVERAGE(C2:C5)</f>
-        <v>-0.00143333333333334</v>
-      </c>
-      <c r="C13" s="31" t="n">
+        <v>-0.00170833333333338</v>
+      </c>
+      <c r="C13" s="32" t="n">
         <f aca="false">AVERAGE(C6:C9)</f>
-        <v>-0.000591666666666733</v>
-      </c>
-      <c r="D13" s="31" t="n">
+        <v>-0.00153333333333329</v>
+      </c>
+      <c r="D13" s="32" t="n">
         <f aca="false">AVERAGE(C4:C5,C8:C9)</f>
-        <v>-0.000516666666666694</v>
-      </c>
-      <c r="E13" s="31" t="n">
+        <v>0.000216666666666647</v>
+      </c>
+      <c r="E13" s="32" t="n">
         <f aca="false">AVERAGE(C2:C3,C6:C7)</f>
-        <v>-0.00150833333333338</v>
+        <v>-0.00345833333333331</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3711,315 +3710,315 @@
       <c r="E15" s="68"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>95</v>
       </c>
       <c r="B17" s="63" t="n">
         <f aca="false">50*SQRT(2)*(1+B13)*Calculator!C4</f>
-        <v>70.6093261466847</v>
+        <v>70.5898807102021</v>
       </c>
       <c r="C17" s="72"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>96</v>
       </c>
       <c r="B18" s="63" t="n">
         <f aca="false">SQRT(((Calculator!E16^2)+(Calculator!E17^2)-2*(B17^2))/2)</f>
-        <v>70.4819895434288</v>
+        <v>70.4637255550487</v>
       </c>
       <c r="C18" s="72"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B19" s="63" t="n">
         <f aca="false">DEGREES(ACOS(((Calculator!E16^2)-(B17^2)-(B18^2))/(2*B17*B18)))</f>
-        <v>89.9961713416085</v>
+        <v>90.0191484094121</v>
       </c>
       <c r="C19" s="72"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B20" s="63" t="n">
         <f aca="false">B19-90</f>
-        <v>-0.003828658391555</v>
+        <v>0.0191484094121108</v>
       </c>
       <c r="C20" s="72"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="43" t="s">
+      <c r="A22" s="44" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="str">
+      <c r="A23" s="1" t="str">
         <f aca="false">"SET_SKEW XY="&amp;ROUND(Calculator!E16,2)&amp;","&amp;ROUND(Calculator!E17,2)&amp;","&amp;ROUND(B17,2)</f>
-        <v>SET_SKEW XY=99.77,99.76,70.61</v>
+        <v>SET_SKEW XY=99.72,99.76,70.59</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="1" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="43" t="s">
+      <c r="A27" s="44" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="1" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="str">
+      <c r="A29" s="1" t="str">
         <f aca="false">" define XY_DIAG_AC " &amp; ROUND(Calculator!E16,4)</f>
-        <v> define XY_DIAG_AC 99.77</v>
+        <v> define XY_DIAG_AC 99.7233</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="str">
+      <c r="A30" s="1" t="str">
         <f aca="false">" define XY_DIAG_BD " &amp; ROUND(Calculator!E17,4)</f>
-        <v> define XY_DIAG_BD 99.7633</v>
+        <v> define XY_DIAG_BD 99.7567</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="str">
+      <c r="A31" s="1" t="str">
         <f aca="false">" define XY_SIDE_AD "&amp;ROUND(B17,4)</f>
-        <v> define XY_SIDE_AD 70.6093</v>
+        <v> define XY_SIDE_AD 70.5899</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="str">
+      <c r="A32" s="1" t="str">
         <f aca="false">IFERROR(" define XY_SKEW_FACTOR " &amp; ROUND(B37,6),"ERROR")</f>
-        <v> define XY_SKEW_FACTOR -0.002576</v>
+        <v> define XY_SKEW_FACTOR -0.002294</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+      <c r="A34" s="1" t="s">
         <v>102</v>
       </c>
       <c r="B34" s="63" t="n">
         <f aca="false">Calculator!E16</f>
-        <v>99.77</v>
+        <v>99.7233333333333</v>
       </c>
       <c r="C34" s="72"/>
-      <c r="F34" s="0" t="s">
+      <c r="F34" s="1" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+      <c r="A35" s="1" t="s">
         <v>104</v>
       </c>
       <c r="B35" s="63" t="n">
         <f aca="false">50*SQRT(2)*(1+C13)*Calculator!C4</f>
-        <v>70.6688409674346</v>
+        <v>70.6022550788728</v>
       </c>
       <c r="C35" s="72"/>
-      <c r="F35" s="0" t="s">
+      <c r="F35" s="1" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
+      <c r="A36" s="1" t="s">
         <v>106</v>
       </c>
       <c r="B36" s="63" t="n">
         <f aca="false">B17</f>
-        <v>70.6093261466847</v>
+        <v>70.5898807102021</v>
       </c>
       <c r="C36" s="72"/>
-      <c r="F36" s="0" t="s">
+      <c r="F36" s="1" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
+      <c r="A37" s="1" t="s">
         <v>108</v>
       </c>
       <c r="B37" s="73" t="n">
         <f aca="false">IFERROR(TAN(PI()/2-ACOS(((B34^2)-(B35^2)-(B36^2))/(2*B35*B36))),"ERROR")</f>
-        <v>-0.0025761352770556</v>
+        <v>-0.00229408364151048</v>
       </c>
       <c r="C37" s="74"/>
       <c r="I37" s="75"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="43" t="s">
+      <c r="A39" s="44" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="43"/>
+      <c r="A40" s="44"/>
       <c r="B40" s="76" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
+      <c r="A41" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B41" s="0" t="str">
+      <c r="B41" s="1" t="str">
         <f aca="false">"M852 I"&amp;ROUND(B37,6)</f>
-        <v>M852 I-0.002576</v>
-      </c>
-      <c r="F41" s="0" t="s">
+        <v>M852 I-0.002294</v>
+      </c>
+      <c r="F41" s="1" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
+      <c r="A42" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B42" s="0" t="s">
+      <c r="B42" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="F42" s="0" t="s">
+      <c r="F42" s="1" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="43" t="s">
+      <c r="A44" s="44" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="s">
+      <c r="A45" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B45" s="0" t="s">
+      <c r="B45" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="F45" s="0" t="s">
+      <c r="F45" s="1" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="s">
+      <c r="A46" s="1" t="s">
         <v>120</v>
       </c>
       <c r="B46" s="77" t="n">
         <f aca="false">100*TAN(RADIANS(B19-90))</f>
-        <v>-0.00668226949662055</v>
+        <v>0.0334202803203744</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="str">
+      <c r="A47" s="1" t="str">
         <f aca="false">"M556 S100 X"&amp; ROUND(B46,3)</f>
-        <v>M556 S100 X-0.007</v>
+        <v>M556 S100 X0.033</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="43" t="s">
+      <c r="A49" s="44" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="43"/>
+      <c r="A50" s="44"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="s">
+      <c r="A51" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B51" s="0" t="str">
+      <c r="B51" s="1" t="str">
         <f aca="false">"M1005 X" &amp; ROUND(Calculator!E16,3) &amp; " Y" &amp; ROUND(Calculator!E17,3)</f>
-        <v>M1005 X99.77 Y99.763</v>
+        <v>M1005 X99.723 Y99.757</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="s">
+      <c r="A52" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B52" s="0" t="s">
+      <c r="B52" s="1" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="s">
+      <c r="A53" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B53" s="0" t="s">
+      <c r="B53" s="1" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="43" t="s">
+      <c r="A55" s="44" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0" t="s">
+      <c r="A56" s="1" t="s">
         <v>125</v>
       </c>
       <c r="B56" s="78" t="n">
         <f aca="false">ROUND((1+AVERAGE(B13,C13))*100,2)</f>
-        <v>99.9</v>
+        <v>99.84</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="s">
+      <c r="A57" s="1" t="s">
         <v>126</v>
       </c>
       <c r="B57" s="72" t="n">
         <f aca="false">ROUND((1-AVERAGE(B13,C13))*100,2)</f>
-        <v>100.1</v>
+        <v>100.16</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="43" t="s">
+      <c r="A59" s="44" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="s">
+      <c r="A60" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B60" s="63" t="n">
         <f aca="false">Calculator!C95*(1-Data!B13)</f>
-        <v>100.143333333333</v>
+        <v>100.170833333333</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="s">
+      <c r="A61" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B61" s="63" t="n">
         <f aca="false">Calculator!C96*(1-Data!C13)</f>
-        <v>100.059166666667</v>
+        <v>100.153333333333</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="43" t="s">
+      <c r="A63" s="44" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0" t="s">
+      <c r="A64" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B64" s="78" t="n">
         <f aca="false">(1+B13)*Calculator!C103</f>
-        <v>99.8566666666667</v>
+        <v>99.8291666666667</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="0" t="s">
+      <c r="A65" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B65" s="78" t="n">
         <f aca="false">(1+C13)*Calculator!C104</f>
-        <v>99.9408333333333</v>
+        <v>99.8466666666667</v>
       </c>
     </row>
   </sheetData>
